--- a/templates/Application-Tracker-Pro-Blank.xlsx
+++ b/templates/Application-Tracker-Pro-Blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\portfolio\academic-application-tracker\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E7BE97-B595-4AE5-B8FC-FFF642A1542B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5280DC83-002C-4304-9195-7C0281776637}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -481,7 +481,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,6 +653,14 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -710,10 +718,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -857,8 +866,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
@@ -1118,7 +1131,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-20B4-4EF6-924B-92E339A5818D}"/>
+                <c16:uniqueId val="{00000001-A86B-4D21-B9D0-E91FA31763A0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1135,7 +1148,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-20B4-4EF6-924B-92E339A5818D}"/>
+                <c16:uniqueId val="{00000003-A86B-4D21-B9D0-E91FA31763A0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1152,7 +1165,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-20B4-4EF6-924B-92E339A5818D}"/>
+                <c16:uniqueId val="{00000005-A86B-4D21-B9D0-E91FA31763A0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1169,7 +1182,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-20B4-4EF6-924B-92E339A5818D}"/>
+                <c16:uniqueId val="{00000007-A86B-4D21-B9D0-E91FA31763A0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1186,7 +1199,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-20B4-4EF6-924B-92E339A5818D}"/>
+                <c16:uniqueId val="{00000009-A86B-4D21-B9D0-E91FA31763A0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1203,13 +1216,19 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-20B4-4EF6-924B-92E339A5818D}"/>
+                <c16:uniqueId val="{0000000B-A86B-4D21-B9D0-E91FA31763A0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.30915248575090676"/>
+                  <c:y val="0.69703978270636779"/>
+                </c:manualLayout>
+              </c:layout>
               <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="square"/>
@@ -1233,9 +1252,12 @@
               <c:showSerName val="0"/>
               <c:showPercent val="1"/>
               <c:showBubbleSize val="1"/>
+              <c:separator>
+</c:separator>
               <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-20B4-4EF6-924B-92E339A5818D}"/>
+                  <c16:uniqueId val="{00000001-A86B-4D21-B9D0-E91FA31763A0}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1266,7 +1288,7 @@
               <c:showBubbleSize val="1"/>
               <c:extLst>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-20B4-4EF6-924B-92E339A5818D}"/>
+                  <c16:uniqueId val="{00000003-A86B-4D21-B9D0-E91FA31763A0}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1274,8 +1296,8 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.32358338560273436"/>
-                  <c:y val="0.57168069000258681"/>
+                  <c:x val="-0.32719111056569128"/>
+                  <c:y val="9.6180683195142211E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr/>
@@ -1306,7 +1328,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-20B4-4EF6-924B-92E339A5818D}"/>
+                  <c16:uniqueId val="{00000005-A86B-4D21-B9D0-E91FA31763A0}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1314,8 +1336,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.34486896288418012"/>
-                  <c:y val="0.28205795858350691"/>
+                  <c:x val="0.22875930622596732"/>
+                  <c:y val="0.64516705469100999"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr/>
@@ -1346,7 +1368,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-20B4-4EF6-924B-92E339A5818D}"/>
+                  <c16:uniqueId val="{00000007-A86B-4D21-B9D0-E91FA31763A0}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1354,8 +1376,8 @@
               <c:idx val="4"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.22118308380375795"/>
-                  <c:y val="0.13076250187204727"/>
+                  <c:x val="-0.37914235003227065"/>
+                  <c:y val="0.42470796062574029"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr/>
@@ -1386,7 +1408,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-20B4-4EF6-924B-92E339A5818D}"/>
+                  <c16:uniqueId val="{00000009-A86B-4D21-B9D0-E91FA31763A0}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1394,8 +1416,8 @@
               <c:idx val="5"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.24962502386211788"/>
-                  <c:y val="1.4048863837492683E-2"/>
+                  <c:x val="0.17752961175197943"/>
+                  <c:y val="1.0806818336532831E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr/>
@@ -1426,7 +1448,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-20B4-4EF6-924B-92E339A5818D}"/>
+                  <c16:uniqueId val="{0000000B-A86B-4D21-B9D0-E91FA31763A0}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1521,7 +1543,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-20B4-4EF6-924B-92E339A5818D}"/>
+              <c16:uniqueId val="{0000000C-A86B-4D21-B9D0-E91FA31763A0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1694,7 +1716,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5B0A-462E-B1E5-5FD5FD034D60}"/>
+              <c16:uniqueId val="{00000000-430C-4752-BE0D-CEAE01EE55DD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1707,11 +1729,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="179877"/>
-        <c:axId val="62360710"/>
+        <c:axId val="11464952"/>
+        <c:axId val="81799968"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="179877"/>
+        <c:axId val="11464952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1744,7 +1766,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62360710"/>
+        <c:crossAx val="81799968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1752,7 +1774,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62360710"/>
+        <c:axId val="81799968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1785,7 +1807,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="179877"/>
+        <c:crossAx val="11464952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1948,7 +1970,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DA26-4167-953B-B3A9B2B5E9F2}"/>
+              <c16:uniqueId val="{00000000-4E25-49FB-AF82-B8DB2BFD02CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2065,7 +2087,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DA26-4167-953B-B3A9B2B5E9F2}"/>
+              <c16:uniqueId val="{00000001-4E25-49FB-AF82-B8DB2BFD02CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2182,7 +2204,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-DA26-4167-953B-B3A9B2B5E9F2}"/>
+              <c16:uniqueId val="{00000002-4E25-49FB-AF82-B8DB2BFD02CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2299,7 +2321,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-DA26-4167-953B-B3A9B2B5E9F2}"/>
+              <c16:uniqueId val="{00000003-4E25-49FB-AF82-B8DB2BFD02CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2311,11 +2333,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="85564515"/>
-        <c:axId val="59640479"/>
+        <c:axId val="64382408"/>
+        <c:axId val="23048054"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="85564515"/>
+        <c:axId val="64382408"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2345,7 +2367,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59640479"/>
+        <c:crossAx val="23048054"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2353,7 +2375,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59640479"/>
+        <c:axId val="23048054"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -2398,7 +2420,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85564515"/>
+        <c:crossAx val="64382408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2620,7 +2642,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-29D5-47D6-BE40-15D11ED79AAE}"/>
+              <c16:uniqueId val="{00000000-9EA7-476C-8112-BB6D3B0ED165}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2633,11 +2655,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="63449552"/>
-        <c:axId val="6790478"/>
+        <c:axId val="52515959"/>
+        <c:axId val="72376031"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="63449552"/>
+        <c:axId val="52515959"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2670,7 +2692,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6790478"/>
+        <c:crossAx val="72376031"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2678,7 +2700,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6790478"/>
+        <c:axId val="72376031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2721,7 +2743,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63449552"/>
+        <c:crossAx val="52515959"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2777,7 +2799,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
+              <a:rPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2918,7 +2940,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3A83-46E0-B6B4-9D5C24ABC327}"/>
+              <c16:uniqueId val="{00000000-D7C7-48B6-9871-2F276C92276E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3035,7 +3057,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3A83-46E0-B6B4-9D5C24ABC327}"/>
+              <c16:uniqueId val="{00000001-D7C7-48B6-9871-2F276C92276E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3152,7 +3174,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3A83-46E0-B6B4-9D5C24ABC327}"/>
+              <c16:uniqueId val="{00000002-D7C7-48B6-9871-2F276C92276E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3269,7 +3291,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-3A83-46E0-B6B4-9D5C24ABC327}"/>
+              <c16:uniqueId val="{00000003-D7C7-48B6-9871-2F276C92276E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3281,11 +3303,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="21821931"/>
-        <c:axId val="29936213"/>
+        <c:axId val="35312347"/>
+        <c:axId val="11152217"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="21821931"/>
+        <c:axId val="35312347"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3315,7 +3337,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29936213"/>
+        <c:crossAx val="11152217"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3323,7 +3345,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29936213"/>
+        <c:axId val="11152217"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -3368,7 +3390,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21821931"/>
+        <c:crossAx val="35312347"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4282,14 +4304,14 @@
       <c r="B40" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="46" t="s">
+      <c r="C40" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="46"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="22" t="s">
@@ -4364,30 +4386,31 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B6" r:id="rId2" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Application%20Tracker%20Pro%20-%20Blank%20Template.xlsx#'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D6" r:id="rId3" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Application%20Tracker%20Pro%20-%20Blank%20Template.xlsx#'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F6" r:id="rId4" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Application%20Tracker%20Pro%20-%20Blank%20Template.xlsx#'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H6" r:id="rId5" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Application%20Tracker%20Pro%20-%20Blank%20Template.xlsx#'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="J6" r:id="rId6" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Application%20Tracker%20Pro%20-%20Blank%20Template.xlsx#'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="L6" r:id="rId7" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Application%20Tracker%20Pro%20-%20Blank%20Template.xlsx#'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="O6" r:id="rId8" location="'Applications'!J4" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="O7" r:id="rId9" location="'Applications'!J4" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="O8" r:id="rId10" location="'Applications'!J4" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="O9" r:id="rId11" location="'Applications'!J4" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="O10" r:id="rId12" location="'Applications'!J4" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="O11" r:id="rId13" location="'Applications'!J4" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O14" r:id="rId14" location="'Applications'!C4" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="I29" r:id="rId15" location="'Applications'!A1" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="I30" r:id="rId16" location="'Universities%20&amp;%20Supervisors'!A1" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="I31" r:id="rId17" location="'Explorer'!A1" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="I32" r:id="rId18" location="'Scoring'!A1" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="I33" r:id="rId19" location="'How%20It%20Works'!A1" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C39" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C40" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B6" location="'Applications'!A4" display="'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D6" location="'Applications'!A4" display="'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F6" location="'Applications'!A4" display="'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H6" location="'Applications'!A4" display="'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="J6" location="'Applications'!A4" display="'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="L6" location="'Applications'!A4" display="'Applications'!A4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="O6" location="'Applications'!J4" display="Not Started" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O7" location="'Applications'!J4" display="In Progress" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="O8" location="'Applications'!J4" display="Submitted" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="O9" location="'Applications'!J4" display="Interview" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="O10" location="'Applications'!J4" display="Accepted" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O11" location="'Applications'!J4" display="Rejected" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="O14" location="'Applications'!C4" display="Germany" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I29" location="'Applications'!A1" display="▶  Applications" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="I30" location="'Universities%20&amp;%20Supervisors'!A1" display="▶  Universities &amp; Supervisors" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I31" location="'Explorer'!A1" display="▶  Explorer (interactive filter)" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="I32" location="'Scoring'!A1" display="▶  Scoring (radar inputs)" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="I33" location="'How%20It%20Works'!A1" display="▶  How It Works" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C40" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C40:H40" r:id="rId4" display="Apply Abroad Lab" xr:uid="{5B311E82-4312-4A46-8F2E-D17BF8D60126}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId22"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -5793,7 +5816,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="O2" r:id="rId2" location="'Dashboard'!A1" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="O2" location="'Dashboard'!A1" display="◀ Back to Dashboard" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6026,8 +6049,8 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="I2" r:id="rId2" location="'Dashboard'!A1" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="I2" location="'Dashboard'!A1" display="◀ Back to Dashboard" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="J4" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6923,11 +6946,11 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="G2" r:id="rId2" location="'Dashboard'!A1" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="G2" location="'Dashboard'!A1" display="◀ Back to Dashboard" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -7214,11 +7237,11 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="G2" r:id="rId2" location="'Dashboard'!A1" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="G2" location="'Dashboard'!A1" display="◀ Back to Dashboard" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -7359,13 +7382,13 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" location="'Dashboard'!A1" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="B6" r:id="rId3" location="'Applications'!A1" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
-    <hyperlink ref="B7" r:id="rId4" location="'Dashboard'!A1" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
-    <hyperlink ref="B8" r:id="rId5" location="'Applications'!A1" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
-    <hyperlink ref="B9" r:id="rId6" location="'Universities%20&amp;%20Supervisors'!A1" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
-    <hyperlink ref="B10" r:id="rId7" location="'Scoring'!A1" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
-    <hyperlink ref="B11" r:id="rId8" location="'Explorer'!A1" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="C3" location="'Dashboard'!A1" display="◀ Back to Dashboard" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="B6" location="'Applications'!A1" display="Data model" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="B7" location="'Dashboard'!A1" display="What is automated" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="B8" location="'Applications'!A1" display="Adding an application" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="B9" location="'Universities%20&amp;%20Supervisors'!A1" display="Adding a university" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="B10" location="'Scoring'!A1" display="Comparing a shortlist" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="B11" location="'Explorer'!A1" display="Filtering" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
